--- a/public/StructureDefinition-pghd-electrocardiogram.xlsx
+++ b/public/StructureDefinition-pghd-electrocardiogram.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-electrocardiogram.xlsx
+++ b/public/StructureDefinition-pghd-electrocardiogram.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5408" uniqueCount="645">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5408" uniqueCount="646">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -6493,7 +6496,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6527,7 +6530,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6604,10 +6607,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6724,10 +6727,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6767,7 +6770,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6844,10 +6847,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6964,10 +6967,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7086,13 +7089,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>301</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -7210,7 +7213,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>306</v>
@@ -7328,7 +7331,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>308</v>
@@ -7448,7 +7451,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>310</v>
@@ -7493,7 +7496,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7570,10 +7573,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7690,10 +7693,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7810,10 +7813,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7930,10 +7933,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8052,10 +8055,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8174,10 +8177,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8200,19 +8203,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8261,7 +8264,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8276,19 +8279,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8296,10 +8299,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8322,16 +8325,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8381,7 +8384,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8405,10 +8408,10 @@
         <v>295</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8416,14 +8419,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8442,19 +8445,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8503,7 +8506,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8518,19 +8521,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8538,14 +8541,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8564,19 +8567,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8625,7 +8628,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8640,19 +8643,19 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8660,10 +8663,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8686,16 +8689,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8745,7 +8748,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8766,13 +8769,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8780,10 +8783,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8806,17 +8809,17 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8865,7 +8868,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8880,19 +8883,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8900,10 +8903,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8926,19 +8929,19 @@
         <v>93</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8987,7 +8990,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8996,7 +8999,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -9005,27 +9008,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9051,16 +9054,16 @@
         <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9085,13 +9088,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9109,7 +9112,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9118,7 +9121,7 @@
         <v>92</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>104</v>
@@ -9133,7 +9136,7 @@
         <v>135</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9144,14 +9147,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9173,16 +9176,16 @@
         <v>190</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -9207,13 +9210,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9231,7 +9234,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9249,27 +9252,27 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9292,19 +9295,19 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9353,7 +9356,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9374,10 +9377,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9388,10 +9391,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9417,13 +9420,13 @@
         <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9452,10 +9455,10 @@
         <v>290</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9473,7 +9476,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9491,27 +9494,27 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9537,16 +9540,16 @@
         <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9574,10 +9577,10 @@
         <v>290</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9595,7 +9598,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9616,10 +9619,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9630,10 +9633,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9656,16 +9659,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9715,7 +9718,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9733,27 +9736,27 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9776,16 +9779,16 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9835,7 +9838,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9853,27 +9856,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9896,19 +9899,19 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
@@ -9957,7 +9960,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9969,7 +9972,7 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9978,10 +9981,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9992,10 +9995,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10110,10 +10113,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10230,14 +10233,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -10259,10 +10262,10 @@
         <v>138</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>141</v>
@@ -10317,7 +10320,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10352,10 +10355,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10378,13 +10381,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10435,7 +10438,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10444,7 +10447,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10456,10 +10459,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10470,10 +10473,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10496,13 +10499,13 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10553,7 +10556,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10562,7 +10565,7 @@
         <v>92</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10574,10 +10577,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10588,10 +10591,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10617,16 +10620,16 @@
         <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10654,10 +10657,10 @@
         <v>116</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10675,7 +10678,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10693,13 +10696,13 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10710,10 +10713,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10739,16 +10742,16 @@
         <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10776,10 +10779,10 @@
         <v>290</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10797,7 +10800,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10815,13 +10818,13 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10832,10 +10835,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10858,17 +10861,17 @@
         <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10917,7 +10920,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10941,7 +10944,7 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10952,10 +10955,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10981,10 +10984,10 @@
         <v>205</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11035,7 +11038,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11056,10 +11059,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11070,10 +11073,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11096,16 +11099,16 @@
         <v>93</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11155,7 +11158,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11176,10 +11179,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11190,10 +11193,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11216,16 +11219,16 @@
         <v>93</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11275,7 +11278,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11296,10 +11299,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11310,10 +11313,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11336,19 +11339,19 @@
         <v>93</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11385,7 +11388,7 @@
         <v>82</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AC75" s="2"/>
       <c r="AD75" t="s" s="2">
@@ -11395,7 +11398,7 @@
         <v>198</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11416,10 +11419,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11430,10 +11433,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11548,10 +11551,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11668,14 +11671,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -11697,10 +11700,10 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>141</v>
@@ -11755,7 +11758,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11790,10 +11793,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11819,13 +11822,13 @@
         <v>190</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O79" t="s" s="2">
         <v>289</v>
@@ -11877,7 +11880,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>92</v>
@@ -11895,7 +11898,7 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>295</v>
@@ -11912,10 +11915,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11938,19 +11941,19 @@
         <v>93</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11999,7 +12002,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12017,27 +12020,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12063,16 +12066,16 @@
         <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12097,13 +12100,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12121,7 +12124,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12130,7 +12133,7 @@
         <v>92</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>104</v>
@@ -12145,7 +12148,7 @@
         <v>135</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12156,14 +12159,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12185,16 +12188,16 @@
         <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12219,13 +12222,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12243,7 +12246,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12261,27 +12264,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12307,16 +12310,16 @@
         <v>83</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12365,7 +12368,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12386,10 +12389,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12400,13 +12403,13 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>82</v>
@@ -12428,19 +12431,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12489,7 +12492,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12510,10 +12513,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12524,10 +12527,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12642,10 +12645,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12762,14 +12765,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12791,10 +12794,10 @@
         <v>138</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>141</v>
@@ -12849,7 +12852,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12884,10 +12887,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12913,13 +12916,13 @@
         <v>190</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O88" t="s" s="2">
         <v>289</v>
@@ -12971,7 +12974,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>92</v>
@@ -12989,7 +12992,7 @@
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>295</v>
@@ -13006,10 +13009,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13124,10 +13127,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13244,10 +13247,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13366,10 +13369,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13484,10 +13487,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13604,10 +13607,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13649,7 +13652,7 @@
       </c>
       <c r="Q94" s="2"/>
       <c r="R94" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="S94" t="s" s="2">
         <v>82</v>
@@ -13726,10 +13729,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13846,10 +13849,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13889,7 +13892,7 @@
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>82</v>
@@ -13966,10 +13969,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14086,10 +14089,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14208,10 +14211,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14330,10 +14333,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14356,19 +14359,19 @@
         <v>93</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
@@ -14405,7 +14408,7 @@
         <v>82</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AC100" s="2"/>
       <c r="AD100" t="s" s="2">
@@ -14415,7 +14418,7 @@
         <v>198</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14433,30 +14436,30 @@
         <v>82</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D101" t="s" s="2">
         <v>82</v>
@@ -14481,16 +14484,16 @@
         <v>190</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14539,7 +14542,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14557,27 +14560,27 @@
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14692,10 +14695,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14812,10 +14815,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14879,7 +14882,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14932,10 +14935,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15054,10 +15057,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15083,16 +15086,16 @@
         <v>190</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
@@ -15117,13 +15120,13 @@
         <v>82</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>82</v>
@@ -15141,7 +15144,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15150,7 +15153,7 @@
         <v>92</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>104</v>
@@ -15165,7 +15168,7 @@
         <v>135</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15176,14 +15179,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15205,16 +15208,16 @@
         <v>190</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15239,13 +15242,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15263,7 +15266,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15281,27 +15284,27 @@
         <v>82</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15327,16 +15330,16 @@
         <v>83</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15385,7 +15388,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15406,10 +15409,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15420,13 +15423,13 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>82</v>
@@ -15448,19 +15451,19 @@
         <v>93</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>82</v>
@@ -15509,7 +15512,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15530,10 +15533,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15544,10 +15547,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15662,10 +15665,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15782,14 +15785,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15811,10 +15814,10 @@
         <v>138</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>141</v>
@@ -15869,7 +15872,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15904,10 +15907,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15933,13 +15936,13 @@
         <v>190</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O113" t="s" s="2">
         <v>289</v>
@@ -15991,7 +15994,7 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>92</v>
@@ -16009,7 +16012,7 @@
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>295</v>
@@ -16026,10 +16029,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16144,10 +16147,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16264,10 +16267,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16386,10 +16389,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16504,10 +16507,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16624,10 +16627,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16669,7 +16672,7 @@
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="S119" t="s" s="2">
         <v>82</v>
@@ -16746,10 +16749,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16866,10 +16869,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16909,7 +16912,7 @@
       </c>
       <c r="Q121" s="2"/>
       <c r="R121" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="S121" t="s" s="2">
         <v>82</v>
@@ -16986,10 +16989,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17106,10 +17109,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17228,10 +17231,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17350,10 +17353,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -17376,19 +17379,19 @@
         <v>93</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>82</v>
@@ -17425,7 +17428,7 @@
         <v>82</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
@@ -17435,7 +17438,7 @@
         <v>198</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17453,30 +17456,30 @@
         <v>82</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>82</v>
@@ -17501,16 +17504,16 @@
         <v>190</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>82</v>
@@ -17559,7 +17562,7 @@
         <v>82</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -17577,27 +17580,27 @@
         <v>82</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17712,10 +17715,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17832,10 +17835,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17899,7 +17902,7 @@
       </c>
       <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>82</v>
@@ -17952,10 +17955,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18070,10 +18073,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18190,10 +18193,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18235,7 +18238,7 @@
       </c>
       <c r="Q132" s="2"/>
       <c r="R132" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="S132" t="s" s="2">
         <v>82</v>
@@ -18312,10 +18315,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18432,10 +18435,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18552,10 +18555,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18672,10 +18675,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18794,10 +18797,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18916,10 +18919,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18945,16 +18948,16 @@
         <v>190</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>82</v>
@@ -18979,13 +18982,13 @@
         <v>82</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>82</v>
@@ -19003,7 +19006,7 @@
         <v>82</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -19012,7 +19015,7 @@
         <v>92</v>
       </c>
       <c r="AI138" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AJ138" t="s" s="2">
         <v>104</v>
@@ -19027,7 +19030,7 @@
         <v>135</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>82</v>
@@ -19038,14 +19041,14 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -19067,16 +19070,16 @@
         <v>190</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>82</v>
@@ -19101,13 +19104,13 @@
         <v>82</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>82</v>
@@ -19125,7 +19128,7 @@
         <v>82</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -19143,27 +19146,27 @@
         <v>82</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19189,16 +19192,16 @@
         <v>83</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>82</v>
@@ -19247,7 +19250,7 @@
         <v>82</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -19268,10 +19271,10 @@
         <v>82</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>82</v>
